--- a/backend/prisma/seed-data/inter-account.xlsx
+++ b/backend/prisma/seed-data/inter-account.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17685"/>
   </bookViews>
   <sheets>
     <sheet name="Inter Accounts" sheetId="11" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -8656,16 +8656,16 @@
         <v>-1150000000</v>
       </c>
       <c r="M162" s="2">
-        <f t="shared" si="17"/>
+        <f>SUM(M5:M160)</f>
         <v>132686063</v>
       </c>
       <c r="N162" s="2">
-        <f t="shared" si="17"/>
+        <f>SUM(N5:N160)</f>
         <v>4183261449</v>
       </c>
       <c r="O162" s="11">
-        <f>SUM(O5:O148)</f>
-        <v>3940089127</v>
+        <f>SUM(O5:O160)</f>
+        <v>3926669655</v>
       </c>
       <c r="P162" s="16">
         <f>SUM(P5:P148)</f>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="O166" s="17">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>-13419472</v>
       </c>
     </row>
   </sheetData>
